--- a/FrontedLRAngular/MaxSoftThinks/ejemplo.xlsx
+++ b/FrontedLRAngular/MaxSoftThinks/ejemplo.xlsx
@@ -4,12 +4,15 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Normalizacion" sheetId="1" r:id="rId1"/>
     <sheet name="Flujo" sheetId="2" r:id="rId2"/>
     <sheet name="Hoja1" sheetId="3" r:id="rId3"/>
+    <sheet name="Hoja2" sheetId="4" r:id="rId4"/>
+    <sheet name="KPIS ANGULAR HTML" sheetId="5" r:id="rId5"/>
+    <sheet name="KPIS ANGULAR TYPESCRIPT" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -21,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="177">
   <si>
     <t>Entidad</t>
   </si>
@@ -1375,13 +1378,2487 @@
   </si>
   <si>
     <t>WALLET</t>
+  </si>
+  <si>
+    <t>Cuenta</t>
+  </si>
+  <si>
+    <t>Tipo de Cuenta</t>
+  </si>
+  <si>
+    <t>Fecha</t>
+  </si>
+  <si>
+    <t>Descripcion</t>
+  </si>
+  <si>
+    <t>Monto</t>
+  </si>
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>Categoria</t>
+  </si>
+  <si>
+    <t>HTML EJEMPLOS KPIS ANGULAR</t>
+  </si>
+  <si>
+    <t>      {{ totalSales | currency:'USD':'symbol' }}</t>
+  </si>
+  <si>
+    <t>          'trend-up': trend === 'up',</t>
+  </si>
+  <si>
+    <t>          'trend-down': trend === 'down',</t>
+  </si>
+  <si>
+    <t>          'trend-neutral': trend === 'neutral'</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF808080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>div</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>class</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"kpi-card"</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF808080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF808080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>h2</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF808080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>📊 Ventas Mensuales</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF808080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;/</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>h2</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF808080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF808080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>div</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>class</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"kpi-value"</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF808080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF808080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;/</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>div</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF808080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF808080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>div</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>class</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"kpi-details"</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF808080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">      </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF808080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>p</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF808080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Meta: {{ targetSales | currency:'USD':'symbol' }}</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF808080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;/</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>p</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF808080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">      </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF808080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>p</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF808080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Progreso: {{ percentageAchieved | number:'1.0-2' }}%</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF808080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;/</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>p</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF808080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF808080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>div</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>class</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"kpi-status"</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>[ngClass]</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"{</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>        }"</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF808080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">      </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF808080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>span</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>*ngIf</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"trend === 'up'"</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF808080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>⬆ Cumplida</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF808080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;/</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>span</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF808080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">      </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF808080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>span</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>*ngIf</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"trend === 'down'"</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF808080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>⬇ Por debajo de la meta</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF808080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;/</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>span</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF808080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">      </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF808080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>span</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>*ngIf</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"trend === 'neutral'"</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF808080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>➡ En progreso</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF808080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;/</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>span</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF808080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF808080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;/</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>div</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF808080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&gt;</t>
+    </r>
+  </si>
+  <si>
+    <t>EJEMPLO KPIS TYPESCRIPT ANGULAR</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>loadKpiData</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>void</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> {</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF6A9955"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>// Simulación de datos traídos desde un servicio (puedes reemplazar con un HttpClient)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>const</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF4FC1FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>salesFromAPI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>55000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">; </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>this</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>totalSales</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF4FC1FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>salesFromAPI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>this</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>percentageAchieved</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>this</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>totalSales</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>this</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>targetSales</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>console</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>log</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>'Percentage Achieved:'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>this</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>percentageAchieved</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>this</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>trend</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>this</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>percentageAchieved</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&gt;=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>'up'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>this</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>percentageAchieved</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&gt;=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>75</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>'neutral'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>'down'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">); </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>console</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>log</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>'Trend:'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>this</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>trend</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <t>  }</t>
+  </si>
+  <si>
+    <t>EN EL NGONINIT</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>this</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>loadKpiData</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>();</t>
+    </r>
+  </si>
+  <si>
+    <t>CONSTANTES DENTRO DEL EXPORT CLASS</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>totalSales</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>number</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>targetSales</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>number</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>50000</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>percentageAchieved</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>number</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>trend</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>'up'</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>|</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>'down'</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>|</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>'neutral'</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>'neutral'</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="8"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1418,8 +3895,139 @@
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFCCCCCC"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF569CD6"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF9CDCFE"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFCE9178"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="8"/>
+      <color rgb="FFCCCCCC"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="8"/>
+      <color rgb="FF808080"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="8"/>
+      <color rgb="FF569CD6"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="8"/>
+      <color rgb="FF9CDCFE"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="8"/>
+      <color rgb="FFCE9178"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFDCDCAA"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFD4D4D4"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF4EC9B0"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF6A9955"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF4FC1FF"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFB5CEA8"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="8"/>
+      <color rgb="FFDCDCAA"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="8"/>
+      <color rgb="FFD4D4D4"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="8"/>
+      <color rgb="FF4EC9B0"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="8"/>
+      <color rgb="FFB5CEA8"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1459,6 +4067,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F1F1F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1649,7 +4263,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1768,6 +4382,21 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4663,4 +7292,249 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A5:G5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C5" t="s">
+        <v>136</v>
+      </c>
+      <c r="D5" t="s">
+        <v>137</v>
+      </c>
+      <c r="E5" t="s">
+        <v>138</v>
+      </c>
+      <c r="F5" t="s">
+        <v>139</v>
+      </c>
+      <c r="G5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="57" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="57" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="58"/>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="57" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="57" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="57" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="58"/>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="57" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="57" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="57" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="57" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="58"/>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="57" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="57" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="59" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="59" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="59" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="59" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="57" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="57" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="57" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="57" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="57" t="s">
+        <v>159</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>170</v>
+      </c>
+      <c r="I2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="57" t="s">
+        <v>171</v>
+      </c>
+      <c r="I3" s="57" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="55" t="s">
+        <v>161</v>
+      </c>
+      <c r="I4" s="57" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="55" t="s">
+        <v>162</v>
+      </c>
+      <c r="I5" s="57" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="55" t="s">
+        <v>163</v>
+      </c>
+      <c r="I6" s="57" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="56"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="55" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="55" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="55" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="55" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="55" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="55" t="s">
+        <v>169</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>